--- a/Indicators/Tobacco.xlsx
+++ b/Indicators/Tobacco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uredu.sharepoint.com/sites/ControlTabacoFacultadEconomica/Documentos compartidos/Monitoreo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uredu.sharepoint.com/sites/ControlTabacoFacultadEconomica/Documentos compartidos/Monitoreo/Repositorio/Indicators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1014" documentId="8_{8E6BD62E-08E8-4FB2-B46B-F5D8EE92EA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{828AE402-24C5-4C90-89DC-422403D56BE8}"/>
+  <xr:revisionPtr revIDLastSave="1021" documentId="8_{8E6BD62E-08E8-4FB2-B46B-F5D8EE92EA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95927384-6A52-40F2-9892-2977088FE92F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{7A94D5C5-EB71-44F3-BD13-919ACF62FAE6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7A94D5C5-EB71-44F3-BD13-919ACF62FAE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Precio" sheetId="4" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="Incautaciones" sheetId="7" r:id="rId6"/>
     <sheet name="Vapeadores" sheetId="8" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1279,42 +1276,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="11" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="9" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="16" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="22" fillId="11" borderId="16" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1325,6 +1287,41 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="9" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1422,7 +1419,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="es-419"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5373,7 +5370,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
+              <a:endParaRPr lang="es-419"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5475,7 +5472,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
+              <a:endParaRPr lang="es-419"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -6883,7 +6880,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
+              <a:endParaRPr lang="es-MX"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -10037,7 +10034,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
+              <a:endParaRPr lang="es-419"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -10139,7 +10136,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-CO"/>
+              <a:endParaRPr lang="es-419"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -11083,7 +11080,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="es-419"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -27599,14 +27596,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>169333</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>121376</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>438785</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>4233</xdr:rowOff>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>159109</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27636,15 +27633,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>712303</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>44726</xdr:rowOff>
+      <xdr:colOff>544746</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133266</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>223629</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>149087</xdr:rowOff>
+      <xdr:colOff>393424</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27673,14 +27670,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>16566</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>16566</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>125812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>240196</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>26505</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>103533</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>155298</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27706,125 +27703,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Tabla dinámica"/>
-      <sheetName val="datos"/>
-      <sheetName val="Gráficos"/>
-      <sheetName val="IHH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v xml:space="preserve">Productos con tabaco (2404110000) </v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>Productos que contengan nicotina (2404120000)</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Otros productos (2404190000)</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>Productos para administración por via oral (2404910000)</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2022</v>
-          </cell>
-          <cell r="B3">
-            <v>6591.4369444404983</v>
-          </cell>
-          <cell r="C3">
-            <v>61209.912447067487</v>
-          </cell>
-          <cell r="D3">
-            <v>9048.4557852929993</v>
-          </cell>
-          <cell r="E3">
-            <v>224.27438783999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2023</v>
-          </cell>
-          <cell r="B4">
-            <v>20236.723411766099</v>
-          </cell>
-          <cell r="C4">
-            <v>43055.644865452101</v>
-          </cell>
-          <cell r="D4">
-            <v>999.45003136740002</v>
-          </cell>
-          <cell r="E4">
-            <v>227.07444587039998</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v xml:space="preserve">Productos con tabaco (2404110000) </v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>Productos que contengan nicotina (2404120000)</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>Otros productos (2404190000)</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>Productos para administración por via oral (2404910000)</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>2022</v>
-          </cell>
-          <cell r="B8">
-            <v>61747.929999999986</v>
-          </cell>
-          <cell r="C8">
-            <v>175725.62</v>
-          </cell>
-          <cell r="D8">
-            <v>28938.770000000004</v>
-          </cell>
-          <cell r="E8">
-            <v>1042.6499999999999</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>2023</v>
-          </cell>
-          <cell r="B9">
-            <v>194319.84999999998</v>
-          </cell>
-          <cell r="C9">
-            <v>106972.69000000002</v>
-          </cell>
-          <cell r="D9">
-            <v>4926.8999999999996</v>
-          </cell>
-          <cell r="E9">
-            <v>1029.47</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35409,10 +35287,10 @@
       <c r="J14" s="37"/>
       <c r="K14" s="37"/>
       <c r="L14" s="37"/>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="S14" s="65"/>
+      <c r="S14" s="71"/>
       <c r="U14" s="43" t="s">
         <v>105</v>
       </c>
@@ -36315,23 +36193,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="K2" s="67" t="s">
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="K2" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="69"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
     </row>
     <row r="3" spans="1:19" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
@@ -36349,22 +36227,22 @@
       <c r="K3" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="M3" s="69"/>
-      <c r="N3" s="67" t="s">
+      <c r="M3" s="78"/>
+      <c r="N3" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="O3" s="69"/>
-      <c r="P3" s="67" t="s">
+      <c r="O3" s="78"/>
+      <c r="P3" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="67" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="76" t="s">
         <v>146</v>
       </c>
-      <c r="S3" s="69"/>
+      <c r="S3" s="78"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54">
@@ -36389,22 +36267,22 @@
       <c r="K4" s="50">
         <v>2010</v>
       </c>
-      <c r="L4" s="72" t="s">
+      <c r="L4" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M4" s="73"/>
-      <c r="N4" s="70">
+      <c r="N4" s="82">
         <v>764</v>
       </c>
-      <c r="O4" s="71"/>
-      <c r="P4" s="70">
+      <c r="O4" s="75"/>
+      <c r="P4" s="82">
         <v>21631006</v>
       </c>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="70">
+      <c r="Q4" s="75"/>
+      <c r="R4" s="82">
         <v>3789125711</v>
       </c>
-      <c r="S4" s="71"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51">
@@ -36424,22 +36302,22 @@
       <c r="K5" s="50">
         <v>2011</v>
       </c>
-      <c r="L5" s="72" t="s">
+      <c r="L5" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M5" s="73"/>
-      <c r="N5" s="70">
+      <c r="N5" s="82">
         <v>1501</v>
       </c>
-      <c r="O5" s="71"/>
-      <c r="P5" s="70">
+      <c r="O5" s="75"/>
+      <c r="P5" s="82">
         <v>46796786</v>
       </c>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="70">
+      <c r="Q5" s="75"/>
+      <c r="R5" s="82">
         <v>8016575326</v>
       </c>
-      <c r="S5" s="71"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
@@ -36459,22 +36337,22 @@
       <c r="K6" s="50">
         <v>2012</v>
       </c>
-      <c r="L6" s="72" t="s">
+      <c r="L6" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M6" s="73"/>
-      <c r="N6" s="70">
+      <c r="N6" s="82">
         <v>1157</v>
       </c>
-      <c r="O6" s="71"/>
-      <c r="P6" s="70">
+      <c r="O6" s="75"/>
+      <c r="P6" s="82">
         <v>5277105</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="70">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="82">
         <v>4770283919</v>
       </c>
-      <c r="S6" s="71"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51">
@@ -36494,22 +36372,22 @@
       <c r="K7" s="50">
         <v>2013</v>
       </c>
-      <c r="L7" s="72" t="s">
+      <c r="L7" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M7" s="73"/>
-      <c r="N7" s="70">
+      <c r="N7" s="82">
         <v>1356</v>
       </c>
-      <c r="O7" s="71"/>
-      <c r="P7" s="70">
+      <c r="O7" s="75"/>
+      <c r="P7" s="82">
         <v>7153203</v>
       </c>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="70">
+      <c r="Q7" s="75"/>
+      <c r="R7" s="82">
         <v>5029517319</v>
       </c>
-      <c r="S7" s="71"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
@@ -36529,22 +36407,22 @@
       <c r="K8" s="50">
         <v>2014</v>
       </c>
-      <c r="L8" s="72" t="s">
+      <c r="L8" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M8" s="73"/>
-      <c r="N8" s="70">
+      <c r="N8" s="82">
         <v>181</v>
       </c>
-      <c r="O8" s="71"/>
-      <c r="P8" s="70">
+      <c r="O8" s="75"/>
+      <c r="P8" s="82">
         <v>6863508</v>
       </c>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="70">
+      <c r="Q8" s="75"/>
+      <c r="R8" s="82">
         <v>9709945832</v>
       </c>
-      <c r="S8" s="71"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51">
@@ -36564,22 +36442,22 @@
       <c r="K9" s="50">
         <v>2015</v>
       </c>
-      <c r="L9" s="72" t="s">
+      <c r="L9" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M9" s="73"/>
-      <c r="N9" s="70">
+      <c r="N9" s="82">
         <v>1725</v>
       </c>
-      <c r="O9" s="71"/>
-      <c r="P9" s="70">
+      <c r="O9" s="75"/>
+      <c r="P9" s="82">
         <v>6185044</v>
       </c>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="70">
+      <c r="Q9" s="75"/>
+      <c r="R9" s="82">
         <v>7725925615</v>
       </c>
-      <c r="S9" s="71"/>
+      <c r="S9" s="75"/>
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
@@ -36599,22 +36477,22 @@
       <c r="K10" s="50">
         <v>2016</v>
       </c>
-      <c r="L10" s="72" t="s">
+      <c r="L10" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M10" s="73"/>
-      <c r="N10" s="70">
+      <c r="N10" s="82">
         <v>1137</v>
       </c>
-      <c r="O10" s="71"/>
-      <c r="P10" s="70">
+      <c r="O10" s="75"/>
+      <c r="P10" s="82">
         <v>4073853</v>
       </c>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="70">
+      <c r="Q10" s="75"/>
+      <c r="R10" s="82">
         <v>5594242294</v>
       </c>
-      <c r="S10" s="71"/>
+      <c r="S10" s="75"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
@@ -36634,22 +36512,22 @@
       <c r="K11" s="50">
         <v>2017</v>
       </c>
-      <c r="L11" s="72" t="s">
+      <c r="L11" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M11" s="73"/>
-      <c r="N11" s="70">
+      <c r="N11" s="82">
         <v>799</v>
       </c>
-      <c r="O11" s="71"/>
-      <c r="P11" s="70">
+      <c r="O11" s="75"/>
+      <c r="P11" s="82">
         <v>7481060</v>
       </c>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="70">
+      <c r="Q11" s="75"/>
+      <c r="R11" s="82">
         <v>6784626043</v>
       </c>
-      <c r="S11" s="71"/>
+      <c r="S11" s="75"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
@@ -36669,170 +36547,232 @@
       <c r="K12" s="50">
         <v>2018</v>
       </c>
-      <c r="L12" s="72" t="s">
+      <c r="L12" s="81" t="s">
         <v>147</v>
       </c>
       <c r="M12" s="73"/>
-      <c r="N12" s="70">
+      <c r="N12" s="82">
         <v>1656</v>
       </c>
-      <c r="O12" s="71"/>
-      <c r="P12" s="70">
+      <c r="O12" s="75"/>
+      <c r="P12" s="82">
         <v>7770767</v>
       </c>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="70">
+      <c r="Q12" s="75"/>
+      <c r="R12" s="82">
         <v>10171851612</v>
       </c>
-      <c r="S12" s="71"/>
+      <c r="S12" s="75"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K13" s="50">
         <v>2019</v>
       </c>
-      <c r="L13" s="74" t="s">
+      <c r="L13" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M13" s="73"/>
-      <c r="N13" s="75">
+      <c r="N13" s="74">
         <v>605</v>
       </c>
-      <c r="O13" s="71"/>
-      <c r="P13" s="75">
+      <c r="O13" s="75"/>
+      <c r="P13" s="74">
         <v>9932435</v>
       </c>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="75">
+      <c r="Q13" s="75"/>
+      <c r="R13" s="74">
         <v>13264828685</v>
       </c>
-      <c r="S13" s="71"/>
+      <c r="S13" s="75"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K14" s="50">
         <v>2020</v>
       </c>
-      <c r="L14" s="74" t="s">
+      <c r="L14" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M14" s="73"/>
-      <c r="N14" s="75">
+      <c r="N14" s="74">
         <v>628</v>
       </c>
-      <c r="O14" s="71"/>
-      <c r="P14" s="75">
+      <c r="O14" s="75"/>
+      <c r="P14" s="74">
         <v>8067906</v>
       </c>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="75">
+      <c r="Q14" s="75"/>
+      <c r="R14" s="74">
         <v>9594533508</v>
       </c>
-      <c r="S14" s="71"/>
+      <c r="S14" s="75"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K15" s="50">
         <v>2021</v>
       </c>
-      <c r="L15" s="74" t="s">
+      <c r="L15" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M15" s="73"/>
-      <c r="N15" s="75">
+      <c r="N15" s="74">
         <v>538</v>
       </c>
-      <c r="O15" s="71"/>
-      <c r="P15" s="75">
+      <c r="O15" s="75"/>
+      <c r="P15" s="74">
         <v>13603099</v>
       </c>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="75">
+      <c r="Q15" s="75"/>
+      <c r="R15" s="74">
         <v>33441410921</v>
       </c>
-      <c r="S15" s="71"/>
+      <c r="S15" s="75"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K16" s="50">
         <v>2022</v>
       </c>
-      <c r="L16" s="74" t="s">
+      <c r="L16" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M16" s="73"/>
-      <c r="N16" s="75">
+      <c r="N16" s="74">
         <v>440</v>
       </c>
-      <c r="O16" s="71"/>
-      <c r="P16" s="75">
+      <c r="O16" s="75"/>
+      <c r="P16" s="74">
         <v>3018565</v>
       </c>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="75">
+      <c r="Q16" s="75"/>
+      <c r="R16" s="74">
         <v>4569187737</v>
       </c>
-      <c r="S16" s="71"/>
+      <c r="S16" s="75"/>
     </row>
     <row r="17" spans="11:19" x14ac:dyDescent="0.3">
       <c r="K17" s="50">
         <v>2023</v>
       </c>
-      <c r="L17" s="74" t="s">
+      <c r="L17" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M17" s="73"/>
-      <c r="N17" s="75">
+      <c r="N17" s="74">
         <v>310</v>
       </c>
-      <c r="O17" s="71"/>
-      <c r="P17" s="75">
+      <c r="O17" s="75"/>
+      <c r="P17" s="74">
         <v>7831050</v>
       </c>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="75">
+      <c r="Q17" s="75"/>
+      <c r="R17" s="74">
         <v>16086707922</v>
       </c>
-      <c r="S17" s="71"/>
+      <c r="S17" s="75"/>
     </row>
     <row r="18" spans="11:19" x14ac:dyDescent="0.3">
       <c r="K18" s="50">
         <v>2024</v>
       </c>
-      <c r="L18" s="74" t="s">
+      <c r="L18" s="72" t="s">
         <v>147</v>
       </c>
       <c r="M18" s="73"/>
-      <c r="N18" s="75">
+      <c r="N18" s="74">
         <v>142</v>
       </c>
-      <c r="O18" s="71"/>
-      <c r="P18" s="75">
+      <c r="O18" s="75"/>
+      <c r="P18" s="74">
         <v>505933</v>
       </c>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="75">
+      <c r="Q18" s="75"/>
+      <c r="R18" s="74">
         <v>943726528</v>
       </c>
-      <c r="S18" s="71"/>
+      <c r="S18" s="75"/>
     </row>
     <row r="19" spans="11:19" x14ac:dyDescent="0.3">
-      <c r="K19" s="67" t="s">
+      <c r="K19" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="L19" s="68"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="76">
+      <c r="L19" s="77"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="79">
         <v>14568</v>
       </c>
-      <c r="O19" s="77"/>
-      <c r="P19" s="76">
+      <c r="O19" s="80"/>
+      <c r="P19" s="79">
         <v>156191320</v>
       </c>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="76">
+      <c r="Q19" s="80"/>
+      <c r="R19" s="79">
         <v>139492488971</v>
       </c>
-      <c r="S19" s="77"/>
+      <c r="S19" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="R17:S17"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="P18:Q18"/>
@@ -36841,68 +36781,6 @@
     <mergeCell ref="N19:O19"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="R19:S19"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -36924,16 +36802,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="69" t="s">
         <v>112</v>
       </c>
     </row>
@@ -36996,122 +36874,122 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
-      <c r="B8" s="79" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="67" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="83">
+      <c r="A10" s="68">
         <v>2022</v>
       </c>
-      <c r="B10" s="78">
+      <c r="B10" s="65">
         <v>6591.4369444404983</v>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="65">
         <v>61209.912447067487</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="65">
         <v>9048.4557852929993</v>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="65">
         <v>224.27438783999997</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="83">
+      <c r="A11" s="68">
         <v>2023</v>
       </c>
-      <c r="B11" s="78">
+      <c r="B11" s="65">
         <v>20236.723411766099</v>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="65">
         <v>43055.644865452101</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="65">
         <v>999.45003136740002</v>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="65">
         <v>227.07444587039998</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="78"/>
-      <c r="B13" s="79" t="s">
+      <c r="A13" s="65"/>
+      <c r="B13" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
     </row>
     <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="D14" s="82" t="s">
+      <c r="D14" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="67" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="83">
+      <c r="A15" s="68">
         <v>2022</v>
       </c>
-      <c r="B15" s="78">
+      <c r="B15" s="65">
         <v>61747.929999999986</v>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="65">
         <v>175725.62</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="65">
         <v>28938.770000000004</v>
       </c>
-      <c r="E15" s="78">
+      <c r="E15" s="65">
         <v>1042.6499999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="83">
+      <c r="A16" s="68">
         <v>2023</v>
       </c>
-      <c r="B16" s="78">
+      <c r="B16" s="65">
         <v>194319.84999999998</v>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="65">
         <v>106972.69000000002</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="65">
         <v>4926.8999999999996</v>
       </c>
-      <c r="E16" s="78">
+      <c r="E16" s="65">
         <v>1029.47</v>
       </c>
     </row>
@@ -37141,17 +37019,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027EAE559E09D4A429EBD0F39DC21BBA6" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c9719185c29a5bbeaf569b57ce7223ff">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57ed4d19-7dfa-4218-b0c9-321a76363151" xmlns:ns3="f52a8275-2cbd-4186-978c-53e036657375" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6164b0d521ef8826ab87409b1a303be5" ns2:_="" ns3:_="">
     <xsd:import namespace="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
@@ -37394,6 +37261,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{561C49FA-4DD9-4C75-A7B3-259135C5DB72}">
   <ds:schemaRefs>
@@ -37403,17 +37281,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B018C194-A9E7-4F06-ABD3-76ED67C36641}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
-    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29AAEE8-4C53-4762-BDD1-44D04E7E4286}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37430,4 +37297,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B018C194-A9E7-4F06-ABD3-76ED67C36641}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
+    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>